--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486737_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486737_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. IBAÑEZ ZAMALLOA</t>
+          <t>A. MARÍN REYES</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7505</v>
+        <v>5.8695</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3283</v>
+        <v>1.1836</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4223</v>
+        <v>4.6859</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8418</v>
+        <v>4.2794</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8214</v>
+        <v>1.7859</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0204</v>
+        <v>2.4936</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1051</v>
+        <v>2.2045</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7877</v>
+        <v>0.4072</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6826</v>
+        <v>1.7973</v>
       </c>
       <c r="M2" t="n">
-        <v>1.7367</v>
+        <v>2.0749</v>
       </c>
       <c r="N2" t="n">
-        <v>1.0337</v>
+        <v>1.3786</v>
       </c>
       <c r="O2" t="n">
-        <v>0.703</v>
+        <v>0.6962</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.7377</v>
+        <v>1.1585</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.8616</v>
+        <v>-0.9654</v>
       </c>
       <c r="R2" t="n">
         <v>2.1239</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5193</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3438</v>
+        <v>-0.0555</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1756</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1271</v>
+        <v>-0.2856</v>
       </c>
       <c r="W2" t="n">
-        <v>2.741</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6138</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. MARÍN REYES</t>
+          <t>A. GUERRERO PAEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9372</v>
+        <v>5.6757</v>
       </c>
       <c r="E3" t="n">
-        <v>0.301</v>
+        <v>1.9943</v>
       </c>
       <c r="F3" t="n">
-        <v>4.6362</v>
+        <v>3.6814</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2794</v>
+        <v>2.7657</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7859</v>
+        <v>1.8206</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4936</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2045</v>
+        <v>0.7532</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4072</v>
+        <v>1.0627</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7973</v>
+        <v>-0.3095</v>
       </c>
       <c r="M3" t="n">
-        <v>2.0749</v>
+        <v>2.0125</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3786</v>
+        <v>0.7579</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6962</v>
+        <v>1.2546</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1585</v>
+        <v>2.1239</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>2.1239</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.215</v>
+        <v>0.7861</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9381</v>
+        <v>0.0134</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7231</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. GUERRERO PAEZ</t>
+          <t>I. IBAÑEZ ZAMALLOA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8673</v>
+        <v>5.1551</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7323</v>
+        <v>0.8321</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1351</v>
+        <v>4.3229</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7657</v>
+        <v>2.8418</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8206</v>
+        <v>2.8214</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.0204</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7532</v>
+        <v>1.1051</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0627</v>
+        <v>1.7877</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.3095</v>
+        <v>-0.6826</v>
       </c>
       <c r="M4" t="n">
-        <v>2.0125</v>
+        <v>1.7367</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7579</v>
+        <v>1.0337</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2546</v>
+        <v>0.703</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1239</v>
+        <v>-1.7377</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.8616</v>
       </c>
       <c r="R4" t="n">
         <v>2.1239</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0222</v>
+        <v>1.9238</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2486</v>
+        <v>0.8476</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2264</v>
+        <v>1.0762</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.1271</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2277</v>
+        <v>2.741</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2277</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.1263</v>
+        <v>3.2945</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3701</v>
+        <v>0.0598</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7562</v>
+        <v>3.2347</v>
       </c>
       <c r="G5" t="n">
         <v>2.9138</v>
@@ -844,13 +844,13 @@
         <v>1.3515</v>
       </c>
       <c r="S5" t="n">
-        <v>1.749</v>
+        <v>0.9173</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4409</v>
+        <v>0.1306</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3082</v>
+        <v>0.7867</v>
       </c>
       <c r="V5" t="n">
         <v>0.0426</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. FORTES SILVA</t>
+          <t>S. GUTIERREZ ROA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1415</v>
+        <v>2.9314</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9391</v>
+        <v>1.4823</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0806</v>
+        <v>1.449</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6804</v>
+        <v>0.0336</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1387</v>
+        <v>-0.1314</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5417</v>
+        <v>0.1651</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6469</v>
+        <v>0.0273</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4841</v>
+        <v>0.1448</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1628</v>
+        <v>-0.1175</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0335</v>
+        <v>0.0063</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3454</v>
+        <v>-0.2763</v>
       </c>
       <c r="O6" t="n">
-        <v>1.379</v>
+        <v>0.2826</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3515</v>
+        <v>0.9654</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1874</v>
+        <v>0.0482</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8829</v>
+        <v>0.2273</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6955</v>
+        <v>-0.1791</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2277</v>
+        <v>1.8842</v>
       </c>
       <c r="W6" t="n">
         <v>1.2277</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. GUTIERREZ ROA</t>
+          <t>A. FORTES SILVA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.984</v>
+        <v>2.5634</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7584</v>
+        <v>-0.3186</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2256</v>
+        <v>2.8819</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0336</v>
+        <v>1.6804</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1314</v>
+        <v>0.1387</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1651</v>
+        <v>1.5417</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0273</v>
+        <v>0.6469</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1448</v>
+        <v>0.4841</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1175</v>
+        <v>0.1628</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0063</v>
+        <v>1.0335</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2763</v>
+        <v>-0.3454</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2826</v>
+        <v>1.379</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9654</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8992</v>
+        <v>0.2345</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4966</v>
+        <v>-0.2624</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4026</v>
+        <v>0.4969</v>
       </c>
       <c r="V7" t="n">
-        <v>1.8842</v>
+        <v>1.2277</v>
       </c>
       <c r="W7" t="n">
         <v>1.2277</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Í. MATEO CASTAÑO</t>
+          <t>A. RELAÑO LOPEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5175</v>
+        <v>1.3798</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2639</v>
+        <v>-0.3093</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7815</v>
+        <v>1.6891</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8944</v>
+        <v>-0.8366</v>
       </c>
       <c r="H8" t="n">
-        <v>0.51</v>
+        <v>-0.7032</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3843</v>
+        <v>-0.1334</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3363</v>
+        <v>-0.512</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3725</v>
+        <v>-0.634</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0361</v>
+        <v>0.1221</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5580000000000001</v>
+        <v>-0.3247</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1376</v>
+        <v>-0.0692</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4205</v>
+        <v>-0.2555</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.1239</v>
+        <v>1.3515</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.8616</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7377</v>
+        <v>1.3515</v>
       </c>
       <c r="S8" t="n">
-        <v>2.747</v>
+        <v>0.5792</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2613</v>
+        <v>-0.083</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4857</v>
+        <v>0.6622</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. RELAÑO LOPEZ</t>
+          <t>J. SANTOLARIA MARTIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0102</v>
+        <v>0.5239</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7782</v>
+        <v>-0.8482</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7884</v>
+        <v>1.3722</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8366</v>
+        <v>0.9927</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7032</v>
+        <v>1.1239</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1334</v>
+        <v>-0.1311</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.512</v>
+        <v>0.0207</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.634</v>
+        <v>0.0207</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1221</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3247</v>
+        <v>0.972</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0692</v>
+        <v>1.1032</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2555</v>
+        <v>-0.1311</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3515</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3515</v>
+        <v>0.3862</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2097</v>
+        <v>0.1105</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5518</v>
+        <v>0.0965</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7615</v>
+        <v>0.014</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SANTOLARIA MARTIN</t>
+          <t>Í. MATEO CASTAÑO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3916</v>
+        <v>-0.078</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0551</v>
+        <v>-2.7601</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4467</v>
+        <v>2.6821</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9927</v>
+        <v>0.8944</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1239</v>
+        <v>0.51</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1311</v>
+        <v>0.3843</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0207</v>
+        <v>0.3363</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0207</v>
+        <v>0.3725</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.0361</v>
       </c>
       <c r="M10" t="n">
-        <v>0.972</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>1.1032</v>
+        <v>0.1376</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1311</v>
+        <v>0.4205</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5792</v>
+        <v>-2.1239</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9654</v>
+        <v>-3.8616</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3862</v>
+        <v>1.7377</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0219</v>
+        <v>1.1515</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1104</v>
+        <v>0.7651</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0885</v>
+        <v>0.3864</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2392</v>
+        <v>-1.1317</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5728</v>
+        <v>-1.3659</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3336</v>
+        <v>0.2342</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6972</v>
@@ -1312,13 +1312,13 @@
         <v>0.3862</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0718</v>
+        <v>0.1793</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2759</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3477</v>
+        <v>0.2484</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2104</v>
+        <v>-2.0118</v>
       </c>
       <c r="E12" t="n">
         <v>0.5476</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.758</v>
+        <v>-2.5594</v>
       </c>
       <c r="G12" t="n">
         <v>0.5815</v>
@@ -1390,13 +1390,13 @@
         <v>0.5792</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-0.7171</v>
       </c>
       <c r="T12" t="n">
         <v>-0.4966</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4191</v>
+        <v>-0.2205</v>
       </c>
       <c r="V12" t="n">
         <v>-2.4554</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.4156</v>
+        <v>-3.035</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.5239</v>
+        <v>-2.3171</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8917</v>
+        <v>-0.7179</v>
       </c>
       <c r="G13" t="n">
         <v>-1.7937</v>
@@ -1468,13 +1468,13 @@
         <v>0.9654</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6565</v>
+        <v>-0.2759</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4966</v>
+        <v>-0.2898</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1599</v>
+        <v>0.0139</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,34 +1501,34 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>20.8609</v>
+        <v>21.1368</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.0953</v>
+        <v>-1.8195</v>
       </c>
       <c r="F14" t="n">
-        <v>22.9565</v>
+        <v>22.9561</v>
       </c>
       <c r="G14" t="n">
         <v>12.6558</v>
       </c>
       <c r="H14" t="n">
-        <v>7.2416</v>
+        <v>7.241599999999998</v>
       </c>
       <c r="I14" t="n">
         <v>5.4145</v>
       </c>
       <c r="J14" t="n">
-        <v>4.251299999999999</v>
+        <v>4.2513</v>
       </c>
       <c r="K14" t="n">
-        <v>3.798799999999999</v>
+        <v>3.7988</v>
       </c>
       <c r="L14" t="n">
         <v>0.4527999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>8.404399999999999</v>
+        <v>8.404400000000001</v>
       </c>
       <c r="N14" t="n">
         <v>3.4428</v>
@@ -1546,16 +1546,16 @@
         <v>15.4463</v>
       </c>
       <c r="S14" t="n">
-        <v>5.3788</v>
+        <v>5.6546</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5484999999999998</v>
+        <v>0.8240999999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>4.830599999999999</v>
+        <v>4.8305</v>
       </c>
       <c r="V14" t="n">
-        <v>2.8262</v>
+        <v>2.826200000000001</v>
       </c>
       <c r="W14" t="n">
         <v>8.5512</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. GONZALEZ GRANDE</t>
+          <t>M. GONZALEZ-MONJE PEREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3518</v>
+        <v>1.7535</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.362</v>
+        <v>-0.2952</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7138</v>
+        <v>2.0486</v>
       </c>
       <c r="G15" t="n">
-        <v>1.039</v>
+        <v>-0.1747</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1862</v>
+        <v>-0.1725</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2252</v>
+        <v>-0.0022</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2016</v>
+        <v>-0.1876</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3237</v>
+        <v>-0.034</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1221</v>
+        <v>-0.1536</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2406</v>
+        <v>0.0129</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1374</v>
+        <v>-0.1385</v>
       </c>
       <c r="O15" t="n">
-        <v>1.1032</v>
+        <v>0.1514</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3862</v>
+        <v>0.9654</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9654</v>
+        <v>-1.1585</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3515</v>
+        <v>2.1239</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5831</v>
+        <v>0.0207</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4614</v>
+        <v>-0.4624</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1217</v>
+        <v>0.4831</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6565</v>
+        <v>0.9421</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.6565</v>
+        <v>1.5133</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. GONZALEZ-MONJE PEREZ</t>
+          <t>P. RODRIGUEZ FAJARDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2294</v>
+        <v>1.5663</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1917</v>
+        <v>0.367</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4211</v>
+        <v>1.1993</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1747</v>
+        <v>1.0905</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1725</v>
+        <v>-0.0828</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0022</v>
+        <v>1.1733</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1876</v>
+        <v>0.6017</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.034</v>
+        <v>-0.0133</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1536</v>
+        <v>0.615</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0129</v>
+        <v>0.4889</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1385</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1514</v>
+        <v>0.5583</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9654</v>
+        <v>1.1585</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1585</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1239</v>
+        <v>1.1585</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4966</v>
+        <v>-0.0689</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.359</v>
+        <v>-0.2347</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8556</v>
+        <v>0.1658</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9421</v>
+        <v>-0.6138</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5712</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ FAJARDO</t>
+          <t>R. GONZALEZ GRANDE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9221</v>
+        <v>1.1894</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5738</v>
+        <v>-1.4996</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3483</v>
+        <v>2.689</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0905</v>
+        <v>1.039</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0828</v>
+        <v>-0.1862</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1733</v>
+        <v>1.2252</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6017</v>
+        <v>-0.2016</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0133</v>
+        <v>-0.3237</v>
       </c>
       <c r="L17" t="n">
-        <v>0.615</v>
+        <v>0.1221</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4889</v>
+        <v>1.2406</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.06950000000000001</v>
+        <v>0.1374</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5583</v>
+        <v>1.1032</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1585</v>
+        <v>0.3862</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1585</v>
+        <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2869</v>
+        <v>0.4207</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0279</v>
+        <v>0.3238</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3148</v>
+        <v>0.0969</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6138</v>
+        <v>-0.6565</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3033</v>
+        <v>0.9116</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1291</v>
+        <v>-0.8188</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4324</v>
+        <v>1.7304</v>
       </c>
       <c r="G18" t="n">
         <v>1.1529</v>
@@ -1858,13 +1858,13 @@
         <v>1.1585</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0426</v>
+        <v>-0.4344</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5518</v>
+        <v>-0.2416</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4908</v>
+        <v>-0.1928</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2715</v>
+        <v>0.1266</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.583</v>
+        <v>-0.4795</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8544</v>
+        <v>0.6061</v>
       </c>
       <c r="G19" t="n">
         <v>0.3816</v>
@@ -1936,13 +1936,13 @@
         <v>1.3515</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4963</v>
+        <v>-0.6412</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5243</v>
+        <v>-0.4209</v>
       </c>
       <c r="U19" t="n">
-        <v>0.028</v>
+        <v>-0.2203</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3658</v>
+        <v>-2.1382</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2763</v>
+        <v>0.3797</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.6421</v>
+        <v>-2.518</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6346000000000001</v>
@@ -2014,13 +2014,13 @@
         <v>0.9654</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8551</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3036</v>
+        <v>-0.2001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5515</v>
+        <v>-0.4274</v>
       </c>
       <c r="V20" t="n">
         <v>-1.8415</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0554</v>
+        <v>-3.1671</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9457</v>
+        <v>-1.256</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1098</v>
+        <v>-1.9111</v>
       </c>
       <c r="G21" t="n">
         <v>-2.1529</v>
@@ -2092,13 +2092,13 @@
         <v>0.9654</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4472</v>
+        <v>-0.5588</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1659</v>
+        <v>-0.4762</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2813</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2277</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9836</v>
+        <v>-3.5492</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0238</v>
+        <v>-3.7135</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0402</v>
+        <v>0.1644</v>
       </c>
       <c r="G22" t="n">
         <v>-5.0144</v>
@@ -2170,13 +2170,13 @@
         <v>1.9308</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5172</v>
+        <v>-1.0827</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2417</v>
+        <v>-0.9314</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2755</v>
+        <v>-0.1513</v>
       </c>
       <c r="V22" t="n">
         <v>2.741</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6525</v>
+        <v>-4.7933</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.1235</v>
+        <v>-5.9167</v>
       </c>
       <c r="F23" t="n">
-        <v>1.471</v>
+        <v>1.1234</v>
       </c>
       <c r="G23" t="n">
         <v>-3.6487</v>
@@ -2248,13 +2248,13 @@
         <v>1.5446</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4246</v>
+        <v>-0.5654</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9381</v>
+        <v>-0.7313</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5135</v>
+        <v>0.1658</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.3933</v>
+        <v>-5.752</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.2061</v>
+        <v>-5.689</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1871</v>
+        <v>-0.063</v>
       </c>
       <c r="G24" t="n">
         <v>-3.6074</v>
@@ -2326,13 +2326,13 @@
         <v>1.3515</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0482</v>
+        <v>-0.4069</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9933</v>
+        <v>-0.4762</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0549</v>
+        <v>0.0693</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.4883</v>
+        <v>-7.0083</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.2414</v>
+        <v>-4.0345</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.2469</v>
+        <v>-2.9738</v>
       </c>
       <c r="G25" t="n">
         <v>-1.0873</v>
@@ -2404,13 +2404,13 @@
         <v>1.5446</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.9143</v>
+        <v>-1.4343</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1865</v>
+        <v>-0.9796</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7279</v>
+        <v>-0.4547</v>
       </c>
       <c r="V25" t="n">
         <v>-2.1698</v>
@@ -2437,10 +2437,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-20.8608</v>
+        <v>-20.8607</v>
       </c>
       <c r="E26" t="n">
-        <v>-22.9562</v>
+        <v>-22.9561</v>
       </c>
       <c r="F26" t="n">
         <v>2.095299999999999</v>
@@ -2482,13 +2482,13 @@
         <v>15.4462</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.3789</v>
+        <v>-5.378699999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.8307</v>
+        <v>-4.8306</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5482999999999998</v>
+        <v>-0.5481999999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-2.8262</v>
